--- a/old/DCOPF-main/DCOPF-main/excel_outputs/pglib_opf_case57_ieee.xlsx
+++ b/old/DCOPF-main/DCOPF-main/excel_outputs/pglib_opf_case57_ieee.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\firda\belajar\ISE711\DCOPF-main\DCOPF-main\excel_outputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\firda\belajar\ISE711\old\DCOPF-main\DCOPF-main\excel_outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47B0255-7F15-4B1E-B2F8-79B336E68E38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{212CC456-3249-498C-A4DC-F4F8C5DAC5AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -204,14 +204,21 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="3">
@@ -252,14 +259,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4558,43 +4566,43 @@
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A20">
+      <c r="A20" s="3">
         <v>4</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>18</v>
       </c>
-      <c r="C20">
-        <v>0</v>
-      </c>
-      <c r="D20">
+      <c r="C20" s="3">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3">
         <v>0.55500000000000005</v>
       </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
+      <c r="E20" s="3">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3">
         <v>53</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>53</v>
       </c>
-      <c r="H20">
+      <c r="H20" s="3">
         <v>53</v>
       </c>
-      <c r="I20">
+      <c r="I20" s="3">
         <v>0.97</v>
       </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>1</v>
-      </c>
-      <c r="L20">
-        <v>-30</v>
-      </c>
-      <c r="M20">
+      <c r="J20" s="3">
+        <v>0</v>
+      </c>
+      <c r="K20" s="3">
+        <v>1</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-30</v>
+      </c>
+      <c r="M20" s="3">
         <v>30</v>
       </c>
       <c r="N20">
@@ -4602,43 +4610,43 @@
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A21">
+      <c r="A21" s="3">
         <v>4</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>18</v>
       </c>
-      <c r="C21">
-        <v>0</v>
-      </c>
-      <c r="D21">
+      <c r="C21" s="3">
+        <v>0</v>
+      </c>
+      <c r="D21" s="3">
         <v>0.43</v>
       </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
+      <c r="E21" s="3">
+        <v>0</v>
+      </c>
+      <c r="F21" s="3">
         <v>69</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="3">
         <v>69</v>
       </c>
-      <c r="H21">
+      <c r="H21" s="3">
         <v>69</v>
       </c>
-      <c r="I21">
+      <c r="I21" s="3">
         <v>0.97799999999999998</v>
       </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="L21">
-        <v>-30</v>
-      </c>
-      <c r="M21">
+      <c r="J21" s="3">
+        <v>0</v>
+      </c>
+      <c r="K21" s="3">
+        <v>1</v>
+      </c>
+      <c r="L21" s="3">
+        <v>-30</v>
+      </c>
+      <c r="M21" s="3">
         <v>30</v>
       </c>
       <c r="N21">
